--- a/output/pdf_financials_xlsx/CBG.xlsx
+++ b/output/pdf_financials_xlsx/CBG.xlsx
@@ -7728,7 +7728,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -10536,7 +10540,11 @@
           <t>Prepaid and deposits 10,419</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CBG.xlsx
+++ b/output/pdf_financials_xlsx/CBG.xlsx
@@ -957,37 +957,37 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5.7e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>3.9e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002892</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003366</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002966</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008343</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000736</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001322</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>2.1e-05</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1758,37 +1758,37 @@
         <v>-0.06390700000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.479406</v>
+        <v>-3.479463</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.053524</v>
+        <v>-4.053579</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.332945</v>
+        <v>-1.332984</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.042044</v>
+        <v>0.039152</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.365746</v>
+        <v>-0.369112</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.194799</v>
+        <v>-0.197765</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.905466</v>
+        <v>-0.913809</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.326932</v>
+        <v>-0.327668</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.908378</v>
+        <v>-0.9097</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.236681</v>
+        <v>-0.236703</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.029796</v>
+        <v>-0.029817</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0.3014</v>
@@ -1856,37 +1856,37 @@
         <v>-0.06390700000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.479406</v>
+        <v>-3.479463</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.053524</v>
+        <v>-4.053579</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.332945</v>
+        <v>-1.332984</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.042044</v>
+        <v>0.039152</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.365746</v>
+        <v>-0.369112</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.194799</v>
+        <v>-0.197765</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.905466</v>
+        <v>-0.913809</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.326932</v>
+        <v>-0.327668</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.908378</v>
+        <v>-0.9097</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.236681</v>
+        <v>-0.236703</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.029796</v>
+        <v>-0.029817</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>0.3014</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.664399793920659</v>
+        <v>8.068418341061308</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-243.8306666666667</v>
+        <v>-246.0746666666667</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-3027.926666666667</v>
+        <v>-3032.333333333333</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-38.98948665487169</v>
+        <v>-38.9931108101964</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-24.15095563084605</v>
+        <v>-24.16797704540665</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>1004.666666666667</v>
@@ -2118,13 +2118,13 @@
         <v>0.534138</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.839882</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.387909</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.362452</v>
       </c>
     </row>
     <row r="35">
@@ -2216,13 +2216,13 @@
         <v>0.534138</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.839882</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.387909</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.362452</v>
       </c>
     </row>
     <row r="37">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -33576,7 +33576,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -34520,7 +34520,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -35860,7 +35860,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -37544,7 +37544,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">

--- a/output/pdf_financials_xlsx/CBG.xlsx
+++ b/output/pdf_financials_xlsx/CBG.xlsx
@@ -1168,16 +1168,16 @@
         <v>-0.365746</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.194799</v>
+        <v>-0.198296</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.905466</v>
+        <v>-1.09565</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.326932</v>
+        <v>-0.377122</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.908378</v>
+        <v>-1.009116</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.236681</v>
@@ -1217,16 +1217,16 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0.003497</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0.190184</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>0.05019</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>0.100738</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>0.065069</v>
@@ -1773,16 +1773,16 @@
         <v>-0.369112</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.197765</v>
+        <v>-0.201262</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.913809</v>
+        <v>-1.103993</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.327668</v>
+        <v>-0.377858</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.9097</v>
+        <v>-1.010438</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.236703</v>
@@ -1871,16 +1871,16 @@
         <v>-0.369112</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.197765</v>
+        <v>-0.201262</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.913809</v>
+        <v>-1.103993</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.327668</v>
+        <v>-0.377858</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.9097</v>
+        <v>-1.010438</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.236703</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-3032.333333333333</v>
+        <v>-3368.126666666667</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-38.9931108101964</v>
@@ -1985,16 +1985,16 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.763525235002219</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-17.35809793273399</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-13.30869055637168</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-9.982796824151039</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-27.49227863664595</v>
@@ -6211,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.003749</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.070892</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -23360,7 +23360,11 @@
           <t>Proceeds - advance for private placement</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -23532,7 +23536,11 @@
           <t>Proceeds from sale of investments (note 6)</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -25250,7 +25258,11 @@
           <t>Proceeds from sale of investments (note 7)</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -28274,7 +28286,11 @@
           <t>Proceeds from sale of investments 8</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -32190,7 +32206,11 @@
           <t>Proceeds from a Private Placement</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -32536,7 +32556,11 @@
           <t>Proceeds from Private Placement</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -36280,7 +36304,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -37202,7 +37230,11 @@
           <t>Income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -37856,7 +37888,11 @@
           <t>Income tax recovery (note 9)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
